--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104583_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104583_W14.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5416</v>
+        <v>4.7066</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5032</v>
+        <v>4.2629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0383</v>
+        <v>0.4437</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9059</v>
+        <v>3.9037</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0592</v>
+        <v>1.057</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8468</v>
+        <v>2.8467</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3531</v>
+        <v>4.3294</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3558</v>
+        <v>3.3436</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4471</v>
+        <v>-0.4257</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8643999999999999</v>
+        <v>1.029</v>
       </c>
       <c r="T2" t="n">
-        <v>0.738</v>
+        <v>0.5269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1264</v>
+        <v>0.5021</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2686</v>
+        <v>2.0562</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8872</v>
+        <v>3.3996</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6186</v>
+        <v>-1.3434</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6382</v>
+        <v>3.6338</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5369</v>
+        <v>3.5247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1014</v>
+        <v>0.1091</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0267</v>
+        <v>4.003</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3177</v>
+        <v>3.2955</v>
       </c>
       <c r="L3" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3885</v>
+        <v>-0.3692</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1087</v>
+        <v>0.8988</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3803</v>
+        <v>0.9217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2716</v>
+        <v>-0.0229</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6063</v>
+        <v>1.3374</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5712</v>
+        <v>-0.6534</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1775</v>
+        <v>1.9908</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0341</v>
+        <v>0.0323</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1646</v>
+        <v>0.1556</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1306</v>
+        <v>-0.1233</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5153</v>
+        <v>1.4909</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4812</v>
+        <v>-1.4587</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7764</v>
+        <v>0.51</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0212</v>
+        <v>-0.0258</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7552</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>1.5425</v>
+        <v>1.5479</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0254</v>
+        <v>0.8334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.8445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2981</v>
+        <v>-0.0111</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3919</v>
+        <v>3.4012</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5367</v>
+        <v>1.542</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8552</v>
+        <v>1.8592</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1831</v>
+        <v>3.1676</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2088</v>
+        <v>0.2336</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.953</v>
+        <v>0.7493</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1875</v>
+        <v>-0.0468</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1405</v>
+        <v>0.7961</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4285</v>
+        <v>-0.0582</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9892</v>
+        <v>-0.486</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5607</v>
+        <v>0.4278</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2667</v>
+        <v>1.2575</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5036</v>
+        <v>2.5017</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2369</v>
+        <v>-1.2442</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9516</v>
+        <v>0.9241</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2685</v>
+        <v>2.258</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3151</v>
+        <v>0.3335</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1195</v>
+        <v>0.5053</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7652</v>
+        <v>-0.2232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.7286</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.146</v>
+        <v>-0.1912</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2819</v>
+        <v>0.5467</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8641</v>
+        <v>-0.7379</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6076</v>
+        <v>-0.6362</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.121</v>
+        <v>-3.1273</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5134</v>
+        <v>2.4911</v>
       </c>
       <c r="J7" t="n">
-        <v>1.798</v>
+        <v>1.7408</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6562</v>
+        <v>-1.6762</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4542</v>
+        <v>3.417</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4056</v>
+        <v>-2.377</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9408</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9506</v>
+        <v>0.0384</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9043</v>
+        <v>-0.0073</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0463</v>
+        <v>0.0457</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3663</v>
+        <v>-0.8253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7008</v>
+        <v>1.2755</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0671</v>
+        <v>-2.1007</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2578</v>
+        <v>1.2585</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4444</v>
+        <v>1.4446</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1866</v>
+        <v>-0.1862</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2572</v>
+        <v>1.2408</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5239</v>
+        <v>1.5168</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0176</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0266</v>
+        <v>0.5018</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>0.0346</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5299</v>
+        <v>0.4672</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9618</v>
+        <v>-2.9433</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1195</v>
+        <v>-1.1952</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8422</v>
+        <v>-1.7481</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2323</v>
+        <v>-2.2252</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3794</v>
+        <v>-1.3841</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8529</v>
+        <v>-0.8411</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7352</v>
+        <v>-0.7521</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4971</v>
+        <v>-1.4731</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1851</v>
+        <v>-0.1718</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1179</v>
+        <v>-0.1652</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0672</v>
+        <v>-0.0066</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1855</v>
+        <v>-4.2783</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1883</v>
+        <v>-2.3764</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9972</v>
+        <v>-1.902</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.3977</v>
+        <v>-6.3909</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4314</v>
+        <v>-2.4271</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9663</v>
+        <v>-3.9638</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.9494</v>
+        <v>-3.9718</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1398</v>
+        <v>-1.1484</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8096</v>
+        <v>-2.8234</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4484</v>
+        <v>-2.4191</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1567</v>
+        <v>-1.1403</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5317</v>
+        <v>0.4297</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6684</v>
+        <v>0.506</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1367</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.624</v>
+        <v>-5.2165</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0745</v>
+        <v>-3.6345</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5495</v>
+        <v>-1.582</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8585</v>
+        <v>0.8642</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5572</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4154</v>
+        <v>1.4214</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2224</v>
+        <v>2.2098</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3565</v>
+        <v>0.348</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3639</v>
+        <v>-1.3457</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5317</v>
+        <v>-0.1231</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.1535</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0944</v>
+        <v>0.0305</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.270199999999999</v>
+        <v>-4.579199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.593900000000001</v>
+        <v>1.9837</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.864100000000001</v>
+        <v>-6.5629</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1155</v>
+        <v>5.0989</v>
       </c>
       <c r="H12" t="n">
-        <v>2.756599999999999</v>
+        <v>2.729899999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3589</v>
+        <v>2.3689</v>
       </c>
       <c r="J12" t="n">
-        <v>14.6228</v>
+        <v>14.3825</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1736</v>
+        <v>7.043599999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>7.449200000000001</v>
+        <v>7.3388</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.507299999999999</v>
+        <v>-9.283799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.4171</v>
+        <v>-4.3137</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.0903</v>
+        <v>-4.970000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.9393</v>
+        <v>-7.9672</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.1466</v>
+        <v>-18.2106</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2076</v>
+        <v>10.2436</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6597</v>
+        <v>4.367400000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6504</v>
+        <v>1.3674</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0092</v>
+        <v>3.0002</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.1061</v>
+        <v>-6.0783</v>
       </c>
       <c r="W12" t="n">
-        <v>4.4673</v>
+        <v>4.4443</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.5733</v>
+        <v>-10.5225</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.0809</v>
+        <v>8.3622</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0026</v>
+        <v>4.688</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0782</v>
+        <v>3.6742</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2551</v>
+        <v>2.2669</v>
       </c>
       <c r="H13" t="n">
-        <v>0.733</v>
+        <v>0.7351</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5221</v>
+        <v>1.5318</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0463</v>
+        <v>2.0333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7029</v>
+        <v>0.6927</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2088</v>
+        <v>0.2336</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0526</v>
+        <v>0.3229</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0948</v>
+        <v>-0.386</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1474</v>
+        <v>0.709</v>
       </c>
       <c r="V13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W13" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1949</v>
+        <v>3.7249</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8895</v>
+        <v>3.9564</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3054</v>
+        <v>-0.2315</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6674</v>
+        <v>2.5962</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8166</v>
+        <v>2.2175</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1492</v>
+        <v>0.3787</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2526</v>
+        <v>2.5494</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9914</v>
+        <v>2.5198</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2612</v>
+        <v>0.0296</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5852000000000001</v>
+        <v>0.0468</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1749</v>
+        <v>-0.3023</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4104</v>
+        <v>0.3492</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3668</v>
+        <v>0.0117</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2642</v>
+        <v>0.2296</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1025</v>
+        <v>-0.2179</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7071</v>
+        <v>-0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8678</v>
+        <v>1.405</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4713</v>
+        <v>3.3026</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8692</v>
+        <v>0.9238</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.398</v>
+        <v>2.3788</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5928</v>
+        <v>1.6885</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2222</v>
+        <v>1.8234</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3706</v>
+        <v>-0.1349</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5731</v>
+        <v>2.2429</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5385</v>
+        <v>1.9822</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0346</v>
+        <v>0.2607</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0197</v>
+        <v>-0.5544</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.1588</v>
       </c>
       <c r="O15" t="n">
-        <v>0.336</v>
+        <v>-0.3956</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2311</v>
+        <v>0.4564</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1089</v>
+        <v>0.3246</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.34</v>
+        <v>0.1317</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4141</v>
+        <v>0.8603</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1388</v>
+        <v>3.0183</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1505</v>
+        <v>1.9333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9883999999999999</v>
+        <v>1.085</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1187</v>
+        <v>3.103</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2264</v>
+        <v>1.2345</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8923</v>
+        <v>1.8684</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3976</v>
+        <v>3.3575</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1855</v>
+        <v>2.151</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2789</v>
+        <v>-0.2546</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.407</v>
+        <v>-0.5203</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8861</v>
+        <v>-0.0585</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5208</v>
+        <v>-0.4618</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9146</v>
+        <v>1.6613</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4785</v>
+        <v>5.0964</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5639</v>
+        <v>-3.4351</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5193</v>
+        <v>3.5255</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8948</v>
+        <v>-0.8851</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4141</v>
+        <v>4.4106</v>
       </c>
       <c r="J17" t="n">
-        <v>6.5699</v>
+        <v>6.5487</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L17" t="n">
-        <v>5.6694</v>
+        <v>5.6523</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0506</v>
+        <v>-3.0232</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.512</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1179</v>
+        <v>-0.4718</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3941</v>
+        <v>-0.3028</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.384</v>
+        <v>0.2916</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8421</v>
+        <v>-1.1187</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2261</v>
+        <v>1.4103</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2254</v>
+        <v>-2.2409</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6827</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.9081</v>
+        <v>-2.9108</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.976</v>
+        <v>-1.0111</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6367</v>
+        <v>0.613</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6127</v>
+        <v>-1.6242</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2494</v>
+        <v>-1.2298</v>
       </c>
       <c r="N18" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0197</v>
+        <v>-0.0593</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0393</v>
+        <v>-0.1955</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1255</v>
+        <v>-0.1716</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7371</v>
+        <v>0.8308</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8626</v>
+        <v>-1.0023</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6833</v>
+        <v>-0.6826</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1977</v>
+        <v>-1.1949</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5144</v>
+        <v>0.5123</v>
       </c>
       <c r="J19" t="n">
-        <v>1.067</v>
+        <v>1.0527</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7503</v>
+        <v>-1.7353</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4007</v>
+        <v>-0.4403</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U19" t="n">
-        <v>0.434</v>
+        <v>0.2777</v>
       </c>
       <c r="V19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6562</v>
+        <v>-0.5918</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3033</v>
+        <v>0.297</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9595</v>
+        <v>-0.8888</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9248</v>
+        <v>-0.924</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1601</v>
+        <v>0.1635</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0849</v>
+        <v>-1.0875</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4424</v>
+        <v>0.4364</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3672</v>
+        <v>-1.3604</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4927</v>
+        <v>-1.4895</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4119</v>
+        <v>-0.3507</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7648</v>
+        <v>-1.8244</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2095</v>
+        <v>-0.096</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5553</v>
+        <v>-1.7284</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6944</v>
+        <v>-1.6802</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1747</v>
+        <v>-1.1665</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2559</v>
+        <v>0.2551</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9503</v>
+        <v>-1.9353</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.244</v>
+        <v>-1.2355</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6847</v>
+        <v>-0.7572</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0587</v>
+        <v>-0.2483</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1183</v>
+        <v>-4.1114</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1747</v>
+        <v>-3.2281</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9436</v>
+        <v>-0.8833</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.1208</v>
+        <v>-6.1347</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.7084</v>
+        <v>-3.7106</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4124</v>
+        <v>-2.4241</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.4456</v>
+        <v>-4.488</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.2276</v>
+        <v>-2.245</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2179</v>
+        <v>-2.243</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6752</v>
+        <v>-1.6467</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7292</v>
+        <v>-0.7003</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3266</v>
+        <v>-0.3256</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4026</v>
+        <v>-0.3747</v>
       </c>
       <c r="V22" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W22" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.249499999999999</v>
+        <v>-8.385400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3404</v>
+        <v>-6.72</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.909</v>
+        <v>-1.6654</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.6202</v>
+        <v>-6.6164</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6219</v>
+        <v>-2.6167</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.9983</v>
+        <v>-3.9997</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6759</v>
+        <v>-3.6931</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5034</v>
+        <v>-1.5103</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9443</v>
+        <v>-2.9233</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7219</v>
+        <v>-0.8585</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3962</v>
+        <v>-0.7506</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.270199999999999</v>
+        <v>5.276299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>6.864000000000002</v>
+        <v>6.5629</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5938</v>
+        <v>-1.2865</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.115599999999999</v>
+        <v>-5.098699999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7565</v>
+        <v>-2.729899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.359099999999999</v>
+        <v>-2.3688</v>
       </c>
       <c r="J24" t="n">
-        <v>9.507300000000003</v>
+        <v>9.283800000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>4.417300000000001</v>
+        <v>4.313699999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>5.090200000000001</v>
+        <v>4.969999999999997</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.6229</v>
+        <v>-14.3826</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.1737</v>
+        <v>-7.0437</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.449299999999999</v>
+        <v>-7.338799999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>7.9393</v>
+        <v>7.967199999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="R24" t="n">
-        <v>18.1468</v>
+        <v>18.2106</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.6594</v>
+        <v>-3.6703</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.0091</v>
+        <v>-3.0001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6505</v>
+        <v>-0.6700999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1061</v>
+        <v>6.0784</v>
       </c>
       <c r="W24" t="n">
-        <v>10.5734</v>
+        <v>10.5227</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.4673</v>
+        <v>-4.4442</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104583_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104583_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>1.5479</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.5225</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104583_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.4442</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
